--- a/tasks/finalpool/canvas-grade-summary/groundtruth_workspace/Canvas_Grade_Summary.xlsx
+++ b/tasks/finalpool/canvas-grade-summary/groundtruth_workspace/Canvas_Grade_Summary.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Environmental Economics &amp; Ethics (Fall 2</t>
+          <t>Environmental Economics &amp; Ethics (Fall 2014)</t>
         </is>
       </c>
     </row>

--- a/tasks/finalpool/canvas-grade-summary/groundtruth_workspace/Canvas_Grade_Summary.xlsx
+++ b/tasks/finalpool/canvas-grade-summary/groundtruth_workspace/Canvas_Grade_Summary.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Students_Submitted</t>
+          <t>Students_Graded</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -458,10 +458,10 @@
         <v>934</v>
       </c>
       <c r="C2" t="n">
-        <v>82.45999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -477,51 +477,51 @@
         <v>827</v>
       </c>
       <c r="C3" t="n">
-        <v>80.63</v>
+        <v>79.64</v>
       </c>
       <c r="D3" t="n">
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Global Governance &amp; Geopolitics (Fall 2013)</t>
+          <t>Environmental Economics &amp; Ethics (Spring 2014)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>818</v>
+        <v>536</v>
       </c>
       <c r="C4" t="n">
-        <v>80.26000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Environmental Economics &amp; Ethics (Spring 2014)</t>
+          <t>Global Governance &amp; Geopolitics (Fall 2013)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>536</v>
+        <v>818</v>
       </c>
       <c r="C5" t="n">
-        <v>79.75</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>98.56</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="6">
@@ -534,10 +534,10 @@
         <v>689</v>
       </c>
       <c r="C6" t="n">
-        <v>79.56999999999999</v>
+        <v>77.38</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>97.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -546,52 +546,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2014)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1366</v>
+        <v>1204</v>
       </c>
       <c r="C7" t="n">
-        <v>79.09999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Global Governance &amp; Geopolitics (Fall 2014)</t>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>602</v>
+        <v>1366</v>
       </c>
       <c r="C8" t="n">
-        <v>79.08</v>
+        <v>77.17</v>
       </c>
       <c r="D8" t="n">
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Spring 2014)</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2013)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1204</v>
+        <v>1710</v>
       </c>
       <c r="C9" t="n">
-        <v>78.97</v>
+        <v>77</v>
       </c>
       <c r="D9" t="n">
         <v>100</v>
@@ -603,20 +603,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Fall 2013)</t>
+          <t>Global Governance &amp; Geopolitics (Fall 2014)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1710</v>
+        <v>602</v>
       </c>
       <c r="C10" t="n">
-        <v>78.92</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>96.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
@@ -629,13 +629,13 @@
         <v>1842</v>
       </c>
       <c r="C11" t="n">
-        <v>78.72</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>98.92</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -648,7 +648,7 @@
         <v>1367</v>
       </c>
       <c r="C12" t="n">
-        <v>77.98</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -667,7 +667,7 @@
         <v>1872</v>
       </c>
       <c r="C13" t="n">
-        <v>77.14</v>
+        <v>74.94</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -686,10 +686,10 @@
         <v>1205</v>
       </c>
       <c r="C14" t="n">
-        <v>76.68000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98.33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>1998</v>
       </c>
       <c r="C15" t="n">
-        <v>74.8</v>
+        <v>70.22</v>
       </c>
       <c r="D15" t="n">
         <v>100</v>
@@ -724,51 +724,51 @@
         <v>1427</v>
       </c>
       <c r="C16" t="n">
-        <v>71.53</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Creative Computing &amp; Culture (Spring 2014)</t>
+          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1414</v>
+        <v>364</v>
       </c>
       <c r="C17" t="n">
-        <v>70.92</v>
+        <v>68.69</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data-Driven Design (Spring 2013)</t>
+          <t>Applied Analytics &amp; Algorithms (Fall 2014)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1064</v>
+        <v>340</v>
       </c>
       <c r="C18" t="n">
-        <v>69.7</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -781,10 +781,10 @@
         <v>1505</v>
       </c>
       <c r="C19" t="n">
-        <v>69.59</v>
+        <v>67.23</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>96.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -793,71 +793,71 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
+          <t>Data-Driven Design (Spring 2014)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>364</v>
+        <v>944</v>
       </c>
       <c r="C20" t="n">
-        <v>69.43000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="D20" t="n">
-        <v>98</v>
+        <v>99.14</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data-Driven Design (Spring 2014)</t>
+          <t>Data-Driven Design (Spring 2013)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>944</v>
+        <v>1064</v>
       </c>
       <c r="C21" t="n">
-        <v>69.33</v>
+        <v>65.81</v>
       </c>
       <c r="D21" t="n">
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied Analytics &amp; Algorithms (Fall 2014)</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2014)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>340</v>
+        <v>1792</v>
       </c>
       <c r="C22" t="n">
-        <v>68.59999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Fall 2014)</t>
+          <t>Creative Computing &amp; Culture (Spring 2014)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1792</v>
+        <v>1414</v>
       </c>
       <c r="C23" t="n">
-        <v>65.73999999999999</v>
+        <v>62.77</v>
       </c>
       <c r="D23" t="n">
         <v>100</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.40000000000001</v>
+        <v>73.13</v>
       </c>
     </row>
   </sheetData>
